--- a/artfynd/A 37906-2022 artfynd.xlsx
+++ b/artfynd/A 37906-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37906-2022 artfynd.xlsx
+++ b/artfynd/A 37906-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2647,6 +2647,541 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115018471</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91526</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570565</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6378174</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115018124</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5348</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570570</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6378137</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115017963</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5348</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570559</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6378132</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115017405</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570601</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6378064</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115017684</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5348</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570582</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6378122</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37906-2022 artfynd.xlsx
+++ b/artfynd/A 37906-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3182,6 +3182,119 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>115082065</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5348</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gallsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570550</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6378171</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37906-2022 artfynd.xlsx
+++ b/artfynd/A 37906-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106860005</v>
+        <v>106870019</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570600.6828388856</v>
+        <v>570601</v>
       </c>
       <c r="R2" t="n">
-        <v>6377980.730964626</v>
+        <v>6378135</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106862259</v>
+        <v>106869671</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +784,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väderums gård, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570555.6781439778</v>
+        <v>570603</v>
       </c>
       <c r="R3" t="n">
-        <v>6377877.406439083</v>
+        <v>6378067</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,67 +859,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106859933</v>
+        <v>109610019</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570594.1954698262</v>
+        <v>570618</v>
       </c>
       <c r="R4" t="n">
-        <v>6377951.62730877</v>
+        <v>6377928</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,22 +936,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,60 +952,56 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106869683</v>
+        <v>106860005</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570578.6640801292</v>
+        <v>570601</v>
       </c>
       <c r="R5" t="n">
-        <v>6378071.615111641</v>
+        <v>6377981</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,22 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,70 +1059,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Katarina Kielatis</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Katarina Kielatis</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106870716</v>
+        <v>116005359</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570609.2497734174</v>
+        <v>570547</v>
       </c>
       <c r="R6" t="n">
-        <v>6378075.90432802</v>
+        <v>6377804</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1136,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1254,12 +1171,7 @@
         <v>106869922</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570584.1289590831</v>
+        <v>570584</v>
       </c>
       <c r="R7" t="n">
-        <v>6378128.616354331</v>
+        <v>6378129</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,19 +1237,9 @@
           <t>2023-02-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,51 +1266,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106869671</v>
+        <v>109610160</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570602.3990502383</v>
+        <v>570596</v>
       </c>
       <c r="R8" t="n">
-        <v>6378067.732479647</v>
+        <v>6378120</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1435,22 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,71 +1347,66 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106869525</v>
+        <v>109610201</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570582.4189130091</v>
+        <v>570551</v>
       </c>
       <c r="R9" t="n">
-        <v>6378072.217170769</v>
+        <v>6378182</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1552,22 +1433,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,56 +1453,47 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106870649</v>
+        <v>115018471</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1639,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570605.7499798049</v>
+        <v>570564</v>
       </c>
       <c r="R10" t="n">
-        <v>6378122.549701437</v>
+        <v>6378174</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,22 +1531,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,67 +1551,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106870519</v>
+        <v>109610223</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570617.893961901</v>
+        <v>570577</v>
       </c>
       <c r="R11" t="n">
-        <v>6378135.645048262</v>
+        <v>6378101</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,22 +1628,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,76 +1642,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106870934</v>
+        <v>116005366</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6436</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570613.0356271303</v>
+        <v>570551</v>
       </c>
       <c r="R12" t="n">
-        <v>6378043.758633317</v>
+        <v>6377793</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,22 +1726,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,70 +1746,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106871066</v>
+        <v>116005367</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6436</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570599.952746629</v>
+        <v>570547</v>
       </c>
       <c r="R13" t="n">
-        <v>6378053.731690144</v>
+        <v>6377791</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,22 +1823,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,63 +1843,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Katarina Kielatis</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Katarina Kielatis</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106870019</v>
+        <v>115778196</v>
       </c>
       <c r="B14" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6443</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Väderum, Väderum, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570600.6959977802</v>
+        <v>570542</v>
       </c>
       <c r="R14" t="n">
-        <v>6378134.809427462</v>
+        <v>6377792</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,22 +1920,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,27 +1940,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109610135</v>
+        <v>116005358</v>
       </c>
       <c r="B15" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,13 +1987,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570563.3279428259</v>
+        <v>570547</v>
       </c>
       <c r="R15" t="n">
-        <v>6378087.45448106</v>
+        <v>6377791</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,22 +2017,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,74 +2033,64 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109610160</v>
+        <v>106862259</v>
       </c>
       <c r="B16" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2671</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Väderums gård, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570596.0988157797</v>
+        <v>570556</v>
       </c>
       <c r="R16" t="n">
-        <v>6378120.771507815</v>
+        <v>6377877</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2362,22 +2114,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,36 +2130,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109610223</v>
+        <v>115017405</v>
       </c>
       <c r="B17" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,34 +2157,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570577.0760436053</v>
+        <v>570601</v>
       </c>
       <c r="R17" t="n">
-        <v>6378101.114510184</v>
+        <v>6378064</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2479,22 +2212,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,78 +2231,63 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109610146</v>
+        <v>109610135</v>
       </c>
       <c r="B18" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101728</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570553.3360679931</v>
+        <v>570564</v>
       </c>
       <c r="R18" t="n">
-        <v>6378167.271460142</v>
+        <v>6378087</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2604,34 +2317,23 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>asphögstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2642,47 +2344,46 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115018124</v>
+        <v>106859933</v>
       </c>
       <c r="B19" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2690,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570569</v>
+        <v>570594</v>
       </c>
       <c r="R19" t="n">
-        <v>6378137</v>
+        <v>6377952</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2720,17 +2421,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,52 +2441,51 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115017405</v>
+        <v>106869525</v>
       </c>
       <c r="B20" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2798,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570601</v>
+        <v>570583</v>
       </c>
       <c r="R20" t="n">
-        <v>6378064</v>
+        <v>6378072</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2828,17 +2523,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,52 +2543,51 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115018471</v>
+        <v>106869683</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2906,10 +2595,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570564</v>
+        <v>570579</v>
       </c>
       <c r="R21" t="n">
-        <v>6378174</v>
+        <v>6378072</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2936,12 +2625,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,52 +2645,51 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Katarina Kielatis</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Katarina Kielatis</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115017684</v>
+        <v>106870519</v>
       </c>
       <c r="B22" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3009,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570582</v>
+        <v>570617</v>
       </c>
       <c r="R22" t="n">
-        <v>6378121</v>
+        <v>6378136</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3039,17 +2727,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,52 +2747,51 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115017963</v>
+        <v>106870649</v>
       </c>
       <c r="B23" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3117,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570559</v>
+        <v>570606</v>
       </c>
       <c r="R23" t="n">
-        <v>6378132</v>
+        <v>6378123</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3147,17 +2829,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,70 +2849,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115082065</v>
+        <v>106870716</v>
       </c>
       <c r="B24" t="n">
-        <v>5348</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gallsjön, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570549</v>
+        <v>570609</v>
       </c>
       <c r="R24" t="n">
-        <v>6378171</v>
+        <v>6378075</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3259,17 +2931,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3278,22 +2945,327 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>106870807</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570633</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6378068</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>106870934</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570612</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6378044</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>106871066</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>570599</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6378053</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-02-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Katarina Kielatis</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Katarina Kielatis</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37906-2022 artfynd.xlsx
+++ b/artfynd/A 37906-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106870019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106869671</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610019</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106860005</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116005359</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106869922</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610201</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115018471</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610223</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116005366</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116005367</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115778196</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116005358</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106862259</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115017405</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610135</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2450,6 +2540,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106859933</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2552,6 +2647,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106869525</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2654,6 +2754,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106869683</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2756,6 +2861,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106870519</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106870649</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2960,6 +3075,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106870716</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3062,6 +3182,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106870807</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3164,6 +3289,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106870934</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3266,8 +3396,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106871066</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>